--- a/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
@@ -314,83 +314,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>1501481</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>3500807781</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>CTY TNHH THƯƠNG MẠI XÂY DỰNG ĐỨC THỊNH</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>4329198.0</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>346336.0</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="n">
-        <v>4675534.0</v>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
@@ -314,6 +314,2316 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>7683399</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>454545.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>45455.0</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>7686385</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>7694503</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>7695105</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>7696548</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>164850.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>16485.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>181335.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>7699316</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>7702005</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>101273.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>10127.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>111400.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>7702852</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>7703068</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>7705193</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>7706365</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>108182.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>10818.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>119000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>7706842</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>7708790</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>7709461</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>258000.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>25800.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>283800.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>7710815</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>7716330</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>772885.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>77289.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>850174.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>7720466</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>7728118</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>159610.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>15961.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>175571.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>7728125</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>236364.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>23636.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>260000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>7728506</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>1514961</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>3819816.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>305585.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4125401.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>1514967</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>1090740.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>87259.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>1177999.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1515080</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>2642262.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>211381.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>2853643.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1535987</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>2867088.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>229367.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>3096455.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>1535989</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>3739680.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>299174.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>4038854.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>1535991</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>2668974.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>213518.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>2882492.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1537215</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>149142.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>11931.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>161073.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>1586533</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>3639510.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>291161.0</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>3930671.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>25387</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>163454.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>16345.0</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>179799.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>56102</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>2367937.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>236794.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>2604731.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
@@ -314,6 +314,2559 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>7683399</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>454545.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>45455.0</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>7686385</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>7694503</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>7695105</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>7696548</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>164850.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>16485.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>181335.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>7699316</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>7702005</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>101273.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>10127.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>111400.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>7702852</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>7703068</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>7705193</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>7706365</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>108182.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>10818.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>119000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>7706842</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>7708790</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>7709461</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>258000.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>25800.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>283800.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>7710815</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>7716330</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>772885.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>77289.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>850174.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>7720466</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>7728118</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>159610.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>15961.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>175571.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>7728125</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>236364.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>23636.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>260000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25DAC</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>7728506</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TCA</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>42322912</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0108269207</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>139073.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>8927.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>148000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TCA</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>42538179</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0108269207</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>44164.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>2836.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>47000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>K25TCA</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>42744822</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0108269207</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>53325.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>3675.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>57000.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1514961</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>3819816.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>305585.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>4125401.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>1514967</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>1090740.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>87259.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>1177999.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>1515080</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>2642262.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>211381.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>2853643.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1535987</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>2867088.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>229367.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>3096455.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>1535989</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>3739680.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>299174.0</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>4038854.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1535991</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>2668974.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>213518.0</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>2882492.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>1537215</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>149142.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>11931.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>161073.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>1586533</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>3639510.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>291161.0</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>3930671.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>25387</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>163454.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>16345.0</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>179799.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>56102</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>2367937.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>236794.0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>2604731.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
@@ -330,12 +330,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7683399</t>
+          <t>14220187</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -351,24 +351,24 @@
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>454545.0</v>
+        <v>3261818.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>45455.0</v>
+        <v>326182.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>500000.0</v>
+        <v>3588000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -402,50 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TVA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>7686385</t>
+          <t>3536581</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0100109106-122</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>90909.0</v>
+        <v>0.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>9091.0</v>
+        <v>0.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -479,50 +479,50 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>7694503</t>
+          <t>847570</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>90909.0</v>
+        <v>206682.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>9091.0</v>
+        <v>20668.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>100000.0</v>
+        <v>227350.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -556,50 +556,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>7695105</t>
+          <t>54554</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H10" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>90909.0</v>
+        <v>1037191.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>9091.0</v>
+        <v>82975.0</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>100000.0</v>
+        <v>1120166.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -633,50 +637,54 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>7696548</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H11" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>164850.0</v>
+        <v>1027822.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>16485.0</v>
+        <v>82226.0</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>181335.0</v>
+        <v>1110048.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -710,50 +718,54 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7699316</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H12" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>90909.0</v>
+        <v>990898.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>9091.0</v>
+        <v>79272.0</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>100000.0</v>
+        <v>1070170.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -787,50 +799,54 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>7702005</t>
+          <t>66977</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H13" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>101273.0</v>
+        <v>1055713.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>10127.0</v>
+        <v>84457.0</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>111400.0</v>
+        <v>1140170.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -864,50 +880,54 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>7702852</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H14" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>109091.0</v>
+        <v>1120417.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>10909.0</v>
+        <v>89633.0</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>120000.0</v>
+        <v>1210050.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -941,50 +961,54 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>7703068</t>
+          <t>78721</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H15" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>90909.0</v>
+        <v>1342628.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>9091.0</v>
+        <v>107410.0</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>100000.0</v>
+        <v>1450038.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1018,50 +1042,54 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>7705193</t>
+          <t>83286</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H16" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>90909.0</v>
+        <v>1111369.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>9091.0</v>
+        <v>88910.0</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>100000.0</v>
+        <v>1200279.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1095,50 +1123,54 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>7706365</t>
+          <t>87050</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H17" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>108182.0</v>
+        <v>1185219.0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>10818.0</v>
+        <v>94818.0</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>119000.0</v>
+        <v>1280037.0</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1172,50 +1204,54 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>7706842</t>
+          <t>90731</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H18" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>109091.0</v>
+        <v>1092926.0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>10909.0</v>
+        <v>87434.0</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>120000.0</v>
+        <v>1180360.0</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1249,50 +1285,54 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>7708790</t>
+          <t>95733</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H19" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>90909.0</v>
+        <v>1014344.0</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>9091.0</v>
+        <v>81147.0</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>100000.0</v>
+        <v>1095491.0</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1326,50 +1366,54 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>7709461</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="H20" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH Thương mại Dịch vụ Phòng cháy Chữa cháy MINH HOÀNG</t>
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>258000.0</v>
+        <v>1065196.0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>25800.0</v>
+        <v>85216.0</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>283800.0</v>
+        <v>1150412.0</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1403,12 +1447,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>7710815</t>
+          <t>1457300</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1418,35 +1462,35 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công Ty TNHH TMDV phòng cháy chữa cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>90909.0</v>
+        <v>4042474.0</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>9091.0</v>
+        <v>323398.0</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>100000.0</v>
+        <v>4365872.0</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1480,50 +1524,50 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>7716330</t>
+          <t>1657483</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH thương mại dịch vụ phòng cháy chữa cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>772885.0</v>
+        <v>1958184.0</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>77289.0</v>
+        <v>156655.0</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>850174.0</v>
+        <v>2114839.0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1557,50 +1601,50 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>7720466</t>
+          <t>1657506</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>Công ty TNHH thương mại dịch vụ phòng cháy chữa cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>90909.0</v>
+        <v>8507248.0</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>9091.0</v>
+        <v>680580.0</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>100000.0</v>
+        <v>9187828.0</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1634,12 +1678,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25THE</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>7728118</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1649,35 +1693,35 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>159610.0</v>
+        <v>153193.0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>15961.0</v>
+        <v>15319.0</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>175571.0</v>
+        <v>168512.0</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1711,12 +1755,12 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25THE</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>7728125</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1726,35 +1770,35 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>236364.0</v>
+        <v>156999.0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>23636.0</v>
+        <v>15700.0</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>260000.0</v>
+        <v>172699.0</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1788,12 +1832,12 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>K25DAC</t>
+          <t>K25THE</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>7728506</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -1803,35 +1847,35 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>0100109106</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education VietNam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>90909.0</v>
+        <v>202500.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>9091.0</v>
+        <v>20250.0</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>100000.0</v>
+        <v>222750.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1865,54 +1909,50 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>K25TCA</t>
+          <t>K25THE</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>42322912</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0108269207</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H27" s="6"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH The Forum Education Vietnam</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ PCCC Minh Hoàng</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>139073.0</v>
+        <v>342945.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>8927.0</v>
+        <v>34295.0</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>148000.0</v>
+        <v>377240.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -1946,54 +1986,54 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>K25TCA</t>
+          <t>K25TDN</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>42538179</t>
+          <t>1896048</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0108269207</t>
+          <t>0303217354-004</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẾ GIỚI DI ĐỘNG</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>217A đường Phạm Văn Thuận, Khu Phố 8, Phường Tam Hiệp, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH The Forum Education Vietnam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>44164.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>2836.0</v>
+        <v>80000.0</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>47000.0</v>
+        <v>1080000.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2011,857 +2051,6 @@
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>K25TCA</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>42744822</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>19/11/2025</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>0108269207</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>Công ty TNHH The Forum Education Vietnam</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>53325.0</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>3675.0</v>
-      </c>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13" t="n">
-        <v>57000.0</v>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q29" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>1514961</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>Công ty TNHH The FORUM EDUCATION</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="n">
-        <v>3819816.0</v>
-      </c>
-      <c r="L30" s="13" t="n">
-        <v>305585.0</v>
-      </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13" t="n">
-        <v>4125401.0</v>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S30" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>1514967</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>1090740.0</v>
-      </c>
-      <c r="L31" s="13" t="n">
-        <v>87259.0</v>
-      </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13" t="n">
-        <v>1177999.0</v>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>1515080</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>2642262.0</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>211381.0</v>
-      </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13" t="n">
-        <v>2853643.0</v>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>1535987</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH The Forum Education Vietnam</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>2867088.0</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>229367.0</v>
-      </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13" t="n">
-        <v>3096455.0</v>
-      </c>
-      <c r="P33" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q33" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>1535989</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="n">
-        <v>3739680.0</v>
-      </c>
-      <c r="L34" s="13" t="n">
-        <v>299174.0</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13" t="n">
-        <v>4038854.0</v>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q34" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>1535991</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>2668974.0</v>
-      </c>
-      <c r="L35" s="13" t="n">
-        <v>213518.0</v>
-      </c>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13" t="n">
-        <v>2882492.0</v>
-      </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q35" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>1537215</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="n">
-        <v>149142.0</v>
-      </c>
-      <c r="L36" s="13" t="n">
-        <v>11931.0</v>
-      </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13" t="n">
-        <v>161073.0</v>
-      </c>
-      <c r="P36" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q36" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>K25TDA</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>1586533</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>03/11/2025</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>0300951119-010</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>3639510.0</v>
-      </c>
-      <c r="L37" s="13" t="n">
-        <v>291161.0</v>
-      </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13" t="n">
-        <v>3930671.0</v>
-      </c>
-      <c r="P37" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q37" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>K25THE</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>25387</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="n">
-        <v>163454.0</v>
-      </c>
-      <c r="L38" s="13" t="n">
-        <v>16345.0</v>
-      </c>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13" t="n">
-        <v>179799.0</v>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q38" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>K25THE</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>56102</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>02/11/2025</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>3502386218</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>2367937.0</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>236794.0</v>
-      </c>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13" t="n">
-        <v>2604731.0</v>
-      </c>
-      <c r="P39" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q39" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuKhongMa.xlsx
@@ -325,54 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TVT</t>
+          <t>K25DAC</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>886453</t>
+          <t>7803316</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0303217354-013</t>
+          <t>0100109106</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẦU TƯ ĐIỆN MÁY XANH</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3501550899</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Một Thành Viên Linh Phong</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>241667.0</v>
+        <v>327727.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>19333.0</v>
+        <v>32773.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>261000.0</v>
+        <v>360500.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -406,54 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TVT</t>
+          <t>K25DAC</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>886467</t>
+          <t>7814847</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0303217354-013</t>
+          <t>0100109106</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẦU TƯ ĐIỆN MÁY XANH</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3501550899</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Một Thành Viên Linh Phong</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1.212963E7</v>
+        <v>231818.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>970370.0</v>
+        <v>23182.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1.31E7</v>
+        <v>255000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -487,54 +479,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TVT</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>886471</t>
+          <t>80918</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0303217354-013</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN ĐẦU TƯ ĐIỆN MÁY XANH</t>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3501550899</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Linh Phong</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1.0095455E7</v>
+        <v>462963.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1009546.0</v>
+        <v>37037.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>1.1105001E7</v>
+        <v>500000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -552,6 +544,798 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25TTA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1354559</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-020</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC ĐẤT ĐỎ</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Một Thành Viên Linh Phong</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>9640060.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>771205.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>1.0411265E7</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25TTA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>1356044</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-020</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC ĐẤT ĐỎ</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Một Thành Viên Linh Phong</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>5317316.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>425385.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>5742701.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>113315</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Cty Trách Nhiệm Hữu Hạn Một Thành Viên Linh Phong</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>272827.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>27283.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>300110.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>115366</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Một Thành Viên Linh Phong</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>174990.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>17499.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>192489.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>7239740</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>720370.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>57630.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>778000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>7381952</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>722223.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>57778.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>780001.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>7574672</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>538889.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>43111.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>582000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>7622774</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>287963.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>23037.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>311000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TVT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>7646455</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>29/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0310471746-364</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CN CÔNG TY CP THƯƠNG MẠI BÁCH HÓA XANH - CH BÁCH HÓA XANH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 290 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh. Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2042391</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3501550899</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LINH PHONG</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>2724800.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>136240.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13" t="n">
+        <v>272480.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>3133520.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
